--- a/stories/arbres/ATOM-SAN.MOV.001-09.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Après le déjeuner, Brice a les jambes qui démangent. Il a envie de bouger. Maman dit : on va dehors. Maman, c'est l'adulte. Ils marchent jusqu'au square. L'air sent la poussière chaude. Une marelle est dessinée au sol. Brice saute dans les cases. Un pied. Puis deux pieds. Maman reste près de lui. Ils jouent dehors, avec un adulte. Parce que Brice a bougé, ses joues sont roses. Il rit. Maman dit : encore un moment dehors. Brice saute encore. Il entend le craquement de la craie. Quand il souffle fort, maman dit : on rentre. Brice a joué dehors, avec un adulte.</t>
+          <t>Après le déjeuner, Brice a les jambes qui démangent. Il a envie de bouger. On va dehors. Maman, c'est l'adulte. Ils marchent jusqu'au square. L'air sent la poussière chaude. Une marelle est dessinée au sol. Brice saute dans les cases. Un pied. Puis deux pieds. Maman reste près de lui. Ils jouent dehors, avec un adulte. Parce que Brice a bougé, ses joues sont roses. Il rit. Encore un moment dehors. Brice saute encore. Il entend le craquement de la craie. Quand il souffle fort, On rentre. Brice a joué dehors, avec un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Après le déjeuner, Brice a les jambes qui démangent. Il a envie de bouger.
+maman|On va dehors. Maman, c'est l'adulte.
+narrateur|Ils marchent jusqu'au square. L'air sent la poussière chaude. Une marelle est dessinée au sol. Brice saute dans les cases. Un pied. Puis deux pieds. Maman reste près de lui. Ils jouent dehors, avec un adulte. Parce que Brice a bougé, ses joues sont roses. Il rit.
+maman|Encore un moment dehors.
+narrateur|Brice saute encore. Il entend le craquement de la craie. Quand il souffle fort,
+maman|On rentre.
+narrateur|Brice a joué dehors, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Brice veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Brice a joué dehors. Maman, l'adulte, était avec lui. Les jambes ont bougé.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Brice boit de l'eau. La craie reste sur ses chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.MOV.001-09.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-09.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 narrateur|Brice a joué dehors, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|Brice veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1681,7 @@
           <t>narrateur|Brice a joué dehors. Maman, l'adulte, était avec lui. Les jambes ont bougé.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1845,7 @@
           <t>narrateur|Brice boit de l'eau. La craie reste sur ses chaussures.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.MOV.001-09.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Brice joue dehors à la marelle</t>
+          <t>La marelle rose du square</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.003</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Les platanes jettent des ronds d'ombre. Une marelle rose attend sur les dalles. Aniss et maman sautent dehors, avec un adulte.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Après le déjeuner, Brice a les jambes qui démangent. Il a envie de bouger. On va dehors. Maman, c'est l'adulte. Ils marchent jusqu'au square. L'air sent la poussière chaude. Une marelle est dessinée au sol. Brice saute dans les cases. Un pied. Puis deux pieds. Maman reste près de lui. Ils jouent dehors, avec un adulte. Parce que Brice a bougé, ses joues sont roses. Il rit. Encore un moment dehors. Brice saute encore. Il entend le craquement de la craie. Quand il souffle fort, On rentre. Brice a joué dehors, avec un adulte.</t>
+          <t>Les platanes jettent des ronds d'ombre. Les ronds bougent sur les dalles. L'air sent la poussière chaude. Une feuille sèche tourne au vent. Elle fait un petit bruit de papier. Une craie rose repose au bord. Elle a déjà dessiné une marelle. Le sac de maman sent le pain. Aniss vit ici, tout près du square. Maman, les ronds bougent ! Oui. Ce sont les feuilles. Tu vois la marelle ? Oui. Elle est rose. En ce moment, les jambes d'Aniss démangent. Elles veulent sauter. On va dehors, Aniss ? Oui, maman. On y va ensemble. On joue dehors, avec un adulte. Ils marchent jusqu'au square. Les chaussures font un bruit de gravier. Un oiseau picore sous un banc. Un oiseau ! Il cherche des miettes. La marelle attend au sol. Les cases sont roses et bleues. Un peu de craie craque sous le pied. Tu sautes dans les cases ? Oui ! Aniss saute. Un pied. Puis deux pieds. Maman reste près de lui. Je reste avec toi. Je joue dehors, avec un adulte. Oui. Bravo. Parce qu'Aniss a bougé, ses joues sont roses. Il rit. Encore un moment dehors ? Oui ! Aniss saute encore. Il entend le craquement de la craie. Tu entends la craie ? Oui. Ça craque. Tu as bien sauté. Un rond d'ombre glisse sur la case. Aniss pose les deux pieds dedans. Bravo, Aniss. Quand il souffle fort, maman s'accroupit. On rentre ensemble ? Oui, maman. Aniss a joué dehors, avec un adulte. La craie reste sur ses chaussures. Ils quittent le square, tout près l'un de l'autre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1329,69 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Après le déjeuner, Brice a les jambes qui démangent. Il a envie de bouger.
-maman|On va dehors. Maman, c'est l'adulte.
-narrateur|Ils marchent jusqu'au square. L'air sent la poussière chaude. Une marelle est dessinée au sol. Brice saute dans les cases. Un pied. Puis deux pieds. Maman reste près de lui. Ils jouent dehors, avec un adulte. Parce que Brice a bougé, ses joues sont roses. Il rit.
-maman|Encore un moment dehors.
-narrateur|Brice saute encore. Il entend le craquement de la craie. Quand il souffle fort,
-maman|On rentre.
-narrateur|Brice a joué dehors, avec un adulte.</t>
+          <t>narrateur|Les platanes jettent des ronds d'ombre.
+narrateur|Les ronds bougent sur les dalles.
+narrateur|L'air sent la poussière chaude.
+narrateur|Une feuille sèche tourne au vent.
+narrateur|Elle fait un petit bruit de papier.
+narrateur|Une craie rose repose au bord.
+narrateur|Elle a déjà dessiné une marelle.
+narrateur|Le sac de maman sent le pain.
+narrateur|Aniss vit ici, tout près du square.
+enfant-m|Maman, les ronds bougent !
+maman|Oui.
+maman|Ce sont les feuilles.
+maman|Tu vois la marelle ?
+enfant-m|Oui.
+enfant-m|Elle est rose.
+narrateur|En ce moment, les jambes d'Aniss démangent.
+narrateur|Elles veulent sauter.
+maman|On va dehors, Aniss ?
+enfant-m|Oui, maman.
+maman|On y va ensemble.
+maman|On joue dehors, avec un adulte.
+narrateur|Ils marchent jusqu'au square.
+narrateur|Les chaussures font un bruit de gravier.
+narrateur|Un oiseau picore sous un banc.
+enfant-m|Un oiseau !
+maman|Il cherche des miettes.
+narrateur|La marelle attend au sol.
+narrateur|Les cases sont roses et bleues.
+narrateur|Un peu de craie craque sous le pied.
+maman|Tu sautes dans les cases ?
+enfant-m|Oui !
+narrateur|Aniss saute.
+narrateur|Un pied.
+narrateur|Puis deux pieds.
+narrateur|Maman reste près de lui.
+maman|Je reste avec toi.
+enfant-m|Je joue dehors, avec un adulte.
+maman|Oui.
+maman|Bravo.
+narrateur|Parce qu'Aniss a bougé, ses joues sont roses.
+narrateur|Il rit.
+maman|Encore un moment dehors ?
+enfant-m|Oui !
+narrateur|Aniss saute encore.
+narrateur|Il entend le craquement de la craie.
+maman|Tu entends la craie ?
+enfant-m|Oui.
+enfant-m|Ça craque.
+maman|Tu as bien sauté.
+narrateur|Un rond d'ombre glisse sur la case.
+narrateur|Aniss pose les deux pieds dedans.
+maman|Bravo, Aniss.
+narrateur|Quand il souffle fort, maman s'accroupit.
+maman|On rentre ensemble ?
+enfant-m|Oui, maman.
+narrateur|Aniss a joué dehors, avec un adulte.
+narrateur|La craie reste sur ses chaussures.
+narrateur|Ils quittent le square, tout près l'un de l'autre.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>enfants_parc,craie</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1418,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Brice veut bouger. Où joue-t-il ?</t>
+          <t>Aniss veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,7 +1574,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Brice veut bouger. Où joue-t-il ?</t>
+          <t>narrateur|Aniss veut bouger.
+narrateur|Où joue-t-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1603,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Brice a joué dehors. Maman, l'adulte, était avec lui. Les jambes ont bougé.</t>
+          <t>Aniss a joué dehors. Maman, l'adulte, était avec lui. Les jambes ont bougé. Tu as joué dehors, avec un adulte ? Oui, maman. Dehors. Bravo, Aniss. Tu as fait du bon travail. La marelle rose reste au soleil. Un rond d'ombre la traverse.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1747,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Brice a joué dehors. Maman, l'adulte, était avec lui. Les jambes ont bougé.</t>
+          <t>narrateur|Aniss a joué dehors.
+narrateur|Maman, l'adulte, était avec lui.
+narrateur|Les jambes ont bougé.
+maman|Tu as joué dehors, avec un adulte ?
+enfant-m|Oui, maman.
+enfant-m|Dehors.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|La marelle rose reste au soleil.
+narrateur|Un rond d'ombre la traverse.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1784,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Brice boit de l'eau. La craie reste sur ses chaussures.</t>
+          <t>Maman tend une gourde. Tu bois un peu d'eau ? Aniss boit une gorgée. La craie reste sur ses chaussures. Merci, maman. Tu as fini de boire ? Oui. Bravo. Le sac de maman sent encore le pain. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1920,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Brice boit de l'eau. La craie reste sur ses chaussures.</t>
+          <t>narrateur|Maman tend une gourde.
+maman|Tu bois un peu d'eau ?
+narrateur|Aniss boit une gorgée.
+narrateur|La craie reste sur ses chaussures.
+enfant-m|Merci, maman.
+maman|Tu as fini de boire ?
+enfant-m|Oui.
+maman|Bravo.
+narrateur|Le sac de maman sent encore le pain.
+narrateur|Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1957,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai sauté dans les cases. J'ai joué dehors. Avec un adulte. Bravo. C'est du bon travail. La craie rose attend le prochain saut. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2097,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai sauté dans les cases.
+enfant-m|J'ai joué dehors.
+maman|Avec un adulte.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|La craie rose attend le prochain saut.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2163,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.MOV.001-09.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-09.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après le déjeuner, Brice a les jambes qui démangent. Il a envie de bouger. Maman dit : on va &lt;emphasis level="moderate"&gt;dehors&lt;/emphasis&gt;. Maman, c'est l'adulte. Ils marchent jusqu'au square. L'air sent la poussière chaude. Une marelle est dessinée au sol. Brice saute dans les cases. Un pied. Puis deux pieds. Maman reste près de lui. Ils jouent dehors, avec un adulte. Parce que Brice a bougé, ses joues sont roses. Il rit. Maman dit : encore un moment dehors. Brice saute encore. Il entend le craquement de la craie. Quand il souffle fort, maman dit : on rentre. Brice a joué dehors, avec un adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les platanes jettent des ronds d'ombre. Les ronds bougent sur les dalles. L'air sent la poussière chaude. Une feuille sèche tourne au vent. Elle fait un petit bruit de papier. Une craie rose repose au bord. Elle a déjà dessiné une marelle. Le sac de maman sent le pain. Aniss vit ici, tout près du square. Maman, les ronds bougent ! Oui. Ce sont les feuilles. Tu vois la marelle ? Oui. Elle est rose. En ce moment, les jambes d'Aniss démangent. Elles veulent sauter. On va dehors, Aniss ? Oui, maman. On y va ensemble. On joue dehors, avec un adulte. Ils marchent jusqu'au square. Les chaussures font un bruit de gravier. Un oiseau picore sous un banc. Un oiseau ! Il cherche des miettes. La marelle attend au sol. Les cases sont roses et bleues. Un peu de craie craque sous le pied. Tu sautes dans les cases ? Oui ! Aniss saute. Un pied. Puis deux pieds. Maman reste près de lui. Je reste avec toi. Je joue dehors, avec un adulte. Oui. Bravo. Parce qu'Aniss a bougé, ses joues sont roses. Il rit. Encore un moment dehors ? Oui ! Aniss saute encore. Il entend le craquement de la craie. Tu entends la craie ? Oui. Ça craque. Tu as bien sauté. Un rond d'ombre glisse sur la case. Aniss pose les deux pieds dedans. Bravo, Aniss. Quand il souffle fort, maman s'accroupit. On rentre ensemble ? Oui, maman. Aniss a joué dehors, avec un adulte. La craie reste sur ses chaussures. Ils quittent le square, tout près l'un de l'autre.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Brice veut bouger. Où joue-t-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1578,7 +1578,6 @@
 narrateur|Où joue-t-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1603,12 +1602,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss a joué dehors. Maman, l'adulte, était avec lui. Les jambes ont bougé. Tu as joué dehors, avec un adulte ? Oui, maman. Dehors. Bravo, Aniss. Tu as fait du bon travail. La marelle rose reste au soleil. Un rond d'ombre la traverse.</t>
+          <t>Aniss a joué dehors. Maman, l'adulte, était avec lui. Les jambes ont bougé. Tu as joué dehors, avec un adulte ? Oui, maman. Dehors. Bravo, Aniss. La marelle rose reste au soleil. Un rond d'ombre la traverse.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Brice a joué &lt;emphasis level="moderate"&gt;dehors&lt;/emphasis&gt;. Maman, l'adulte, était avec lui. Les jambes ont bougé.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a joué dehors. Maman, l'adulte, était avec lui. Les jambes ont bougé. Tu as joué dehors, avec un adulte ? Oui, maman. Dehors. Bravo, Aniss. La marelle rose reste au soleil. Un rond d'ombre la traverse.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1754,12 +1753,10 @@
 enfant-m|Oui, maman.
 enfant-m|Dehors.
 maman|Bravo, Aniss.
-maman|Tu as fait du bon travail.
 narrateur|La marelle rose reste au soleil.
 narrateur|Un rond d'ombre la traverse.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1789,7 +1786,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Brice boit de l'eau. La craie reste sur ses chaussures.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman tend une gourde. Tu bois un peu d'eau ? Aniss boit une gorgée. La craie reste sur ses chaussures. Merci, maman. Tu as fini de boire ? Oui. Bravo. Le sac de maman sent encore le pain. Ils marchent vers la maison.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1932,7 +1929,6 @@
 narrateur|Ils marchent vers la maison.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,12 +1953,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai sauté dans les cases. J'ai joué dehors. Avec un adulte. Bravo. C'est du bon travail. La craie rose attend le prochain saut. L'histoire est finie.</t>
+          <t>J'ai sauté dans les cases. J'ai joué dehors. Avec un adulte. Bravo. La craie rose attend le prochain saut.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai sauté dans les cases. J'ai joué dehors. Avec un adulte. Bravo. La craie rose attend le prochain saut.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2101,12 +2097,9 @@
 enfant-m|J'ai joué dehors.
 maman|Avec un adulte.
 maman|Bravo.
-maman|C'est du bon travail.
-narrateur|La craie rose attend le prochain saut.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La craie rose attend le prochain saut.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2125,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2170,6 +2163,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.MOV.001-09.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-09.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>square, marelle</t>
+          <t>square, marelle à la craie, platanes</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Brice, maman</t>
+          <t>Aniss, maman</t>
         </is>
       </c>
     </row>
